--- a/Data/TM_CM_Linking.xlsx
+++ b/Data/TM_CM_Linking.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F23198D-7CC9-439F-882F-A24A61638EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TM_CM_Linking_RP" sheetId="1" r:id="rId1"/>
+    <sheet name="ClientCmLinking_RP" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +25,56 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+  <si>
+    <t>RequestNo</t>
+  </si>
+  <si>
+    <t>CE_CC_Id</t>
+  </si>
+  <si>
+    <t>TM_ID</t>
+  </si>
+  <si>
+    <t>TM_client_ID</t>
+  </si>
+  <si>
+    <t>UCC_ID</t>
+  </si>
+  <si>
+    <t>Client_Id</t>
+  </si>
+  <si>
+    <t>TMID</t>
+  </si>
+  <si>
+    <t>TM0521</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +85,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +93,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +398,138 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B2" s="1">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1">
+        <v>10690</v>
+      </c>
+      <c r="D2" s="4">
+        <v>100673000090921</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6FEC31-B426-425D-955E-5D0E2CD2925A}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="1">
+        <v>100110</v>
+      </c>
+      <c r="C2" s="4">
+        <v>100673000090921</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/TM_CM_Linking.xlsx
+++ b/Data/TM_CM_Linking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F23198D-7CC9-439F-882F-A24A61638EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DB0284-2A13-4A72-B1CF-0714F58B855B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TM_CM_Linking_RP" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>RequestNo</t>
   </si>
@@ -50,13 +50,16 @@
   </si>
   <si>
     <t>TM0521</t>
+  </si>
+  <si>
+    <t>CeCcID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +78,20 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,13 +129,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6FEC31-B426-425D-955E-5D0E2CD2925A}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -483,7 +503,7 @@
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -496,38 +516,66 @@
       <c r="D1" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1111</v>
+      </c>
+      <c r="B2" s="6">
         <v>100110</v>
       </c>
-      <c r="C2" s="4">
-        <v>100673000090921</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="8">
+        <v>102905240000023</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="C3" s="8">
+        <v>102905240000023</v>
+      </c>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
+      <c r="C4" s="4">
+        <v>100673000090921</v>
+      </c>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/TM_CM_Linking.xlsx
+++ b/Data/TM_CM_Linking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DB0284-2A13-4A72-B1CF-0714F58B855B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66463F9E-C22A-4E46-93F5-6848AA997326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TM_CM_Linking_RP" sheetId="1" r:id="rId1"/>
@@ -129,14 +129,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -516,7 +515,7 @@
       <c r="D1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="1"/>
@@ -524,16 +523,16 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="1">
         <v>1111</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="1">
         <v>100110</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>102905240000023</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1">
@@ -546,7 +545,7 @@
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>102905240000023</v>
       </c>
       <c r="D3" s="1"/>

--- a/Data/TM_CM_Linking.xlsx
+++ b/Data/TM_CM_Linking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66463F9E-C22A-4E46-93F5-6848AA997326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C32C75E-B86F-486B-9BBB-0E073B3F1809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TM_CM_Linking_RP" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>RequestNo</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>TMID</t>
-  </si>
-  <si>
-    <t>TM0521</t>
   </si>
   <si>
     <t>CeCcID</t>
@@ -423,6 +420,7 @@
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -445,16 +443,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="B2" s="1">
         <v>11</v>
       </c>
-      <c r="C2" s="1">
-        <v>10690</v>
+      <c r="C2" s="4">
+        <v>24032026</v>
       </c>
       <c r="D2" s="4">
-        <v>100673000090921</v>
+        <v>120484000090143</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -500,6 +498,7 @@
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -516,7 +515,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -524,19 +523,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B2" s="1">
-        <v>100110</v>
+        <v>2403</v>
       </c>
       <c r="C2" s="7">
-        <v>102905240000023</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>120484000001272</v>
+      </c>
+      <c r="D2" s="4">
+        <v>24032026</v>
       </c>
       <c r="E2" s="1">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
